--- a/files/login_testcases.xlsx
+++ b/files/login_testcases.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>

--- a/files/login_testcases.xlsx
+++ b/files/login_testcases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,31 +447,26 @@
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>实际结果</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC01</t>
+          <t>T01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>User123</t>
+          <t>user01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Passw0rd</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>账号和密码均合法</t>
+          <t>合法账号与合法密码</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -481,29 +476,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>登录成功并跳转主页</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>格式校验通过并登录成功</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC02</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user@name</t>
+          <t>user@01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Qwer1234</t>
+          <t>Pwd1234</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,107 +509,92 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>提示账号格式错误</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC03</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>用户01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Passw0rd3</t>
+          <t>Pwd12345</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>账号长度为合法最小值1</t>
+          <t>账号含中文</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>健壮边界值(合法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>登录成功并跳转主页</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
+          <t>提示账号格式错误</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC04</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12345678901234567890</t>
+          <t>user02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Passw0rd4</t>
+          <t>pwd@123</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>账号长度为合法最大值20</t>
+          <t>密码含特殊字符</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>健壮边界值(合法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>登录成功并跳转主页</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
+          <t>提示密码格式错误</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC05</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UserDomain</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ab1234</t>
+          <t>Ab1c2D</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>密码长度为合法最小值6</t>
+          <t>账号长度1和密码长度6均合法</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -629,34 +604,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>登录成功并跳转主页</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
+          <t>格式校验通过并登录成功</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC06</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AnotherUse</t>
+          <t>abcde12345fghij67890</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Abcdefghij123456</t>
+          <t>Abcd1234Efgh5678</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>密码长度为合法最大值16</t>
+          <t>账号长度20和密码长度16均合法</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -666,104 +636,89 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>登录成功并跳转主页</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
+          <t>格式校验通过并登录成功</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>abc123</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Passw0rd7</t>
+          <t>A1b2C3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>账号为空即长度0</t>
+          <t>密码长度6合法且账号合法</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>健壮边界值(非法边界)</t>
+          <t>健壮边界值(合法边界)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>提示账号不能为空</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
+          <t>格式校验通过并登录成功</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC08</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12345678901234567890x</t>
+          <t>b2c3d4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Passw0rd8</t>
+          <t>Zyxw9876Vuts5432</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>账号长度为非法值21</t>
+          <t>密码长度16合法且账号合法</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>健壮边界值(非法边界)</t>
+          <t>健壮边界值(合法边界)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>提示账号长度超出范围</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
+          <t>格式校验通过并登录成功</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TC09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>UserAccount</t>
-        </is>
-      </c>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ab123</t>
+          <t>Ab12c</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>密码长度为非法值5</t>
+          <t>账号长度0和密码长度5均非法</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -773,34 +728,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>提示密码长度不足</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
+          <t>提示账号和密码格式错误</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TC10</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AnotherUser</t>
+          <t>abcdefghij12345678901</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Abcdefghij1234567</t>
+          <t>Abcd1234Efgh56789</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>密码长度为非法值17</t>
+          <t>账号长度21和密码长度17均非法</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -810,12 +760,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>提示密码长度超出范围</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>失败(Message: invalid session id; For documentation on )</t>
+          <t>提示账号和密码格式错误</t>
         </is>
       </c>
     </row>
